--- a/dat/xls/Datasets.xlsx
+++ b/dat/xls/Datasets.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dateien\Studium_KIT\Master_GOEK\Masterarbeit\dat\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BD5287B-859A-4B90-8B57-B20F13E80CB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53E105C4-F842-43A1-A96E-94033B184CB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{494D2F2E-8213-468D-9C63-A165A8562F7F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="79">
   <si>
     <t>Block</t>
   </si>
@@ -262,6 +262,18 @@
   </si>
   <si>
     <t>B8_4_0174</t>
+  </si>
+  <si>
+    <t>Available</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Availability</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
 </sst>
 </file>
@@ -333,7 +345,47 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="10">
+    <dxf>
+      <font>
+        <color theme="4" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF9999FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -356,11 +408,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF7030A0"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FF9999FF"/>
+          <bgColor rgb="FFCCCCFF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -381,36 +443,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="4" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7030A0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCCCCFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -730,13 +762,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE79BF54-AF13-4A80-A00E-8AA827B7DF27}">
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -747,10 +781,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -762,10 +799,13 @@
         <v>ortho_B1_1</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -777,10 +817,13 @@
         <v>ortho_B1_2</v>
       </c>
       <c r="D3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -792,10 +835,13 @@
         <v>ortho_B1_3</v>
       </c>
       <c r="D4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="E4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
@@ -807,10 +853,13 @@
         <v>ortho_B1_4</v>
       </c>
       <c r="D5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="E5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1</v>
       </c>
@@ -822,10 +871,13 @@
         <v>ortho_B1_5</v>
       </c>
       <c r="D6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="E6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1</v>
       </c>
@@ -837,10 +889,13 @@
         <v>ortho_B1_6</v>
       </c>
       <c r="D7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="E7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2</v>
       </c>
@@ -852,10 +907,13 @@
         <v>ortho_B2_1</v>
       </c>
       <c r="D8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="E8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2</v>
       </c>
@@ -867,10 +925,13 @@
         <v>ortho_B2_2</v>
       </c>
       <c r="D9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="E9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2</v>
       </c>
@@ -882,10 +943,13 @@
         <v>ortho_B2_3</v>
       </c>
       <c r="D10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="E10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2</v>
       </c>
@@ -897,10 +961,13 @@
         <v>ortho_B2_4</v>
       </c>
       <c r="D11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="E11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2</v>
       </c>
@@ -912,10 +979,13 @@
         <v>ortho_B2_5</v>
       </c>
       <c r="D12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="E12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2</v>
       </c>
@@ -927,10 +997,13 @@
         <v>ortho_B2_6</v>
       </c>
       <c r="D13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="E13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>3</v>
       </c>
@@ -942,10 +1015,13 @@
         <v>ortho_B3_1</v>
       </c>
       <c r="D14" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="E14" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>3</v>
       </c>
@@ -957,10 +1033,13 @@
         <v>ortho_B3_2</v>
       </c>
       <c r="D15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>3</v>
       </c>
@@ -972,10 +1051,13 @@
         <v>ortho_B3_3</v>
       </c>
       <c r="D16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="E16" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>3</v>
       </c>
@@ -987,10 +1069,13 @@
         <v>ortho_B3_4</v>
       </c>
       <c r="D17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="E17" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>3</v>
       </c>
@@ -1002,10 +1087,13 @@
         <v>ortho_B3_5</v>
       </c>
       <c r="D18" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="E18" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>3</v>
       </c>
@@ -1017,10 +1105,13 @@
         <v>ortho_B3_6</v>
       </c>
       <c r="D19" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="E19" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>4</v>
       </c>
@@ -1032,10 +1123,13 @@
         <v>ortho_B4_1</v>
       </c>
       <c r="D20" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="E20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>4</v>
       </c>
@@ -1047,10 +1141,13 @@
         <v>ortho_B4_2</v>
       </c>
       <c r="D21" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>4</v>
       </c>
@@ -1062,10 +1159,13 @@
         <v>ortho_B4_3</v>
       </c>
       <c r="D22" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>4</v>
       </c>
@@ -1077,10 +1177,13 @@
         <v>ortho_B4_4</v>
       </c>
       <c r="D23" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>4</v>
       </c>
@@ -1092,10 +1195,13 @@
         <v>ortho_B4_5</v>
       </c>
       <c r="D24" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>4</v>
       </c>
@@ -1107,10 +1213,13 @@
         <v>ortho_B4_6</v>
       </c>
       <c r="D25" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>5</v>
       </c>
@@ -1122,10 +1231,13 @@
         <v>ortho_B5_1</v>
       </c>
       <c r="D26" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>5</v>
       </c>
@@ -1137,10 +1249,13 @@
         <v>ortho_B5_2</v>
       </c>
       <c r="D27" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>5</v>
       </c>
@@ -1152,10 +1267,13 @@
         <v>ortho_B5_3</v>
       </c>
       <c r="D28" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="E28" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>5</v>
       </c>
@@ -1167,10 +1285,13 @@
         <v>ortho_B5_4</v>
       </c>
       <c r="D29" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="E29" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>5</v>
       </c>
@@ -1182,10 +1303,13 @@
         <v>ortho_B5_5</v>
       </c>
       <c r="D30" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="E30" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>5</v>
       </c>
@@ -1197,10 +1321,13 @@
         <v>ortho_B5_6</v>
       </c>
       <c r="D31" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="E31" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>6</v>
       </c>
@@ -1212,10 +1339,13 @@
         <v>ortho_B6_1</v>
       </c>
       <c r="D32" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="E32" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>6</v>
       </c>
@@ -1227,10 +1357,13 @@
         <v>ortho_B6_2</v>
       </c>
       <c r="D33" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="E33" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>6</v>
       </c>
@@ -1242,10 +1375,13 @@
         <v>ortho_B6_3</v>
       </c>
       <c r="D34" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="E34" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>6</v>
       </c>
@@ -1257,10 +1393,13 @@
         <v>ortho_B6_4</v>
       </c>
       <c r="D35" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="E35" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>6</v>
       </c>
@@ -1272,10 +1411,13 @@
         <v>ortho_B6_5</v>
       </c>
       <c r="D36" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="E36" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>6</v>
       </c>
@@ -1287,10 +1429,13 @@
         <v>ortho_B6_6</v>
       </c>
       <c r="D37" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="E37" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>7</v>
       </c>
@@ -1302,10 +1447,13 @@
         <v>ortho_B7_1</v>
       </c>
       <c r="D38" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="E38" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>7</v>
       </c>
@@ -1317,10 +1465,13 @@
         <v>ortho_B7_2</v>
       </c>
       <c r="D39" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="E39" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>7</v>
       </c>
@@ -1332,10 +1483,13 @@
         <v>ortho_B7_3</v>
       </c>
       <c r="D40" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="E40" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>7</v>
       </c>
@@ -1347,10 +1501,13 @@
         <v>ortho_B7_4</v>
       </c>
       <c r="D41" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="E41" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>7</v>
       </c>
@@ -1362,10 +1519,13 @@
         <v>ortho_B7_5</v>
       </c>
       <c r="D42" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="E42" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>7</v>
       </c>
@@ -1377,10 +1537,13 @@
         <v>ortho_B7_6</v>
       </c>
       <c r="D43" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="E43" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>8</v>
       </c>
@@ -1392,10 +1555,13 @@
         <v>ortho_B8_1</v>
       </c>
       <c r="D44" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="E44" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>8</v>
       </c>
@@ -1407,10 +1573,13 @@
         <v>ortho_B8_2</v>
       </c>
       <c r="D45" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="E45" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>8</v>
       </c>
@@ -1422,10 +1591,13 @@
         <v>ortho_B8_3</v>
       </c>
       <c r="D46" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="E46" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>8</v>
       </c>
@@ -1437,10 +1609,13 @@
         <v>ortho_B8_4</v>
       </c>
       <c r="D47" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="E47" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>8</v>
       </c>
@@ -1452,10 +1627,13 @@
         <v>ortho_B8_5</v>
       </c>
       <c r="D48" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="E48" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>8</v>
       </c>
@@ -1467,6 +1645,9 @@
         <v>ortho_B8_6</v>
       </c>
       <c r="D49" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1476,8 +1657,50 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{90A337FB-AE1B-449F-954B-B16E92568F33}">
-            <xm:f>NOT(ISERROR(SEARCH(Dropdown_options!$A$2,D2)))</xm:f>
+          <x14:cfRule type="containsText" priority="3" operator="containsText" id="{EEA13BC5-0DC5-435F-8716-C97768FCEDE2}">
+            <xm:f>NOT(ISERROR(SEARCH(Dropdown_options!$A$5,E2)))</xm:f>
+            <xm:f>Dropdown_options!$A$5</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{25424193-5861-463E-B2DB-F16901AB5210}">
+            <xm:f>NOT(ISERROR(SEARCH(Dropdown_options!$A$4,E2)))</xm:f>
+            <xm:f>Dropdown_options!$A$4</xm:f>
+            <x14:dxf>
+              <font>
+                <color theme="4" tint="-0.499984740745262"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor theme="8" tint="0.39994506668294322"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="5" operator="containsText" id="{192BF5E7-0BE2-40B8-971C-EEE4C3DC45A2}">
+            <xm:f>NOT(ISERROR(SEARCH(Dropdown_options!$A$3,E2)))</xm:f>
+            <xm:f>Dropdown_options!$A$3</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF7030A0"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFCCCCFF"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="6" operator="containsText" id="{90A337FB-AE1B-449F-954B-B16E92568F33}">
+            <xm:f>NOT(ISERROR(SEARCH(Dropdown_options!$A$2,E2)))</xm:f>
             <xm:f>Dropdown_options!$A$2</xm:f>
             <x14:dxf>
               <font>
@@ -1490,37 +1713,11 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="3" operator="containsText" id="{192BF5E7-0BE2-40B8-971C-EEE4C3DC45A2}">
-            <xm:f>NOT(ISERROR(SEARCH(Dropdown_options!$A$3,D2)))</xm:f>
-            <xm:f>Dropdown_options!$A$3</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FF7030A0"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFCCCCFF"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="containsText" priority="2" operator="containsText" id="{25424193-5861-463E-B2DB-F16901AB5210}">
-            <xm:f>NOT(ISERROR(SEARCH(Dropdown_options!$A$4,D2)))</xm:f>
-            <xm:f>Dropdown_options!$A$4</xm:f>
-            <x14:dxf>
-              <font>
-                <color theme="4" tint="-0.499984740745262"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor theme="8" tint="0.39994506668294322"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{EEA13BC5-0DC5-435F-8716-C97768FCEDE2}">
-            <xm:f>NOT(ISERROR(SEARCH(Dropdown_options!$A$5,D2)))</xm:f>
-            <xm:f>Dropdown_options!$A$5</xm:f>
+          <xm:sqref>E2:E49</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="1" operator="equal" id="{E41D9CF8-BA7C-40E7-BB3B-85FB93697E09}">
+            <xm:f>Dropdown_options!$B$3</xm:f>
             <x14:dxf>
               <font>
                 <color rgb="FF9C0006"/>
@@ -1532,15 +1729,34 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{D2C351E5-31D5-4C72-9547-D9A432E311C1}">
+            <xm:f>Dropdown_options!$B$2</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF006100"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
           <xm:sqref>D2:D49</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{05AC515E-0B30-4D07-984A-FD88CAB847DB}">
           <x14:formula1>
             <xm:f>Dropdown_options!$A$2:$A$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E49</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1A5D075D-2EFE-46E5-9A14-1DC8C60CBF16}">
+          <x14:formula1>
+            <xm:f>Dropdown_options!$B$2:$B$3</xm:f>
           </x14:formula1>
           <xm:sqref>D2:D49</xm:sqref>
         </x14:dataValidation>
@@ -2101,16 +2317,30 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{D90AEFBD-B16A-404D-B9FE-6C2E8EA5536C}">
-            <xm:f>NOT(ISERROR(SEARCH(Dropdown_options!$A$4,B2)))</xm:f>
-            <xm:f>Dropdown_options!$A$4</xm:f>
+          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{7A67E0E9-BC46-4111-B070-728168ED54EB}">
+            <xm:f>NOT(ISERROR(SEARCH(Dropdown_options!$A$2,B2)))</xm:f>
+            <xm:f>Dropdown_options!$A$2</xm:f>
             <x14:dxf>
               <font>
-                <color theme="4" tint="-0.499984740745262"/>
+                <color rgb="FF006100"/>
               </font>
               <fill>
                 <patternFill>
-                  <bgColor theme="8" tint="0.39994506668294322"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="2" operator="containsText" id="{F891952C-C388-4833-AD9E-FF872CD81D43}">
+            <xm:f>NOT(ISERROR(SEARCH(Dropdown_options!$A$5,B2)))</xm:f>
+            <xm:f>Dropdown_options!$A$5</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFC7CE"/>
                 </patternFill>
               </fill>
             </x14:dxf>
@@ -2129,30 +2359,16 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="containsText" priority="2" operator="containsText" id="{F891952C-C388-4833-AD9E-FF872CD81D43}">
-            <xm:f>NOT(ISERROR(SEARCH(Dropdown_options!$A$5,B2)))</xm:f>
-            <xm:f>Dropdown_options!$A$5</xm:f>
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{D90AEFBD-B16A-404D-B9FE-6C2E8EA5536C}">
+            <xm:f>NOT(ISERROR(SEARCH(Dropdown_options!$A$4,B2)))</xm:f>
+            <xm:f>Dropdown_options!$A$4</xm:f>
             <x14:dxf>
               <font>
-                <color rgb="FF9C0006"/>
+                <color theme="4" tint="-0.499984740745262"/>
               </font>
               <fill>
                 <patternFill>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{7A67E0E9-BC46-4111-B070-728168ED54EB}">
-            <xm:f>NOT(ISERROR(SEARCH(Dropdown_options!$A$2,B2)))</xm:f>
-            <xm:f>Dropdown_options!$A$2</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FF006100"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFC6EFCE"/>
+                  <bgColor theme="8" tint="0.39994506668294322"/>
                 </patternFill>
               </fill>
             </x14:dxf>
@@ -2177,36 +2393,47 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D377B6CC-8542-42B9-B5B1-181F4556A626}">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B1" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="B5" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dat/xls/Datasets.xlsx
+++ b/dat/xls/Datasets.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dateien\Studium_KIT\Master_GOEK\Masterarbeit\dat\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53E105C4-F842-43A1-A96E-94033B184CB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E910C757-D2E9-493E-8736-69C73A04739E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{494D2F2E-8213-468D-9C63-A165A8562F7F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="79">
   <si>
     <t>Block</t>
   </si>
@@ -1768,557 +1768,1095 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B035F39-13CE-40F5-A10F-A2C3B444467D}">
-  <dimension ref="A1:B67"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="str">
+        <f>RIGHT(LEFT(C2,2),1)</f>
+        <v>1</v>
+      </c>
+      <c r="B2" t="str">
+        <f>LEFT(RIGHT(C2,6),1)</f>
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="str">
+        <f>RIGHT(LEFT(C3,2),1)</f>
+        <v>1</v>
+      </c>
+      <c r="B3" t="str">
+        <f>LEFT(RIGHT(C3,6),1)</f>
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="str">
+        <f>RIGHT(LEFT(C4,2),1)</f>
+        <v>1</v>
+      </c>
+      <c r="B4" t="str">
+        <f>LEFT(RIGHT(C4,6),1)</f>
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="str">
+        <f>RIGHT(LEFT(C5,2),1)</f>
+        <v>1</v>
+      </c>
+      <c r="B5" t="str">
+        <f>LEFT(RIGHT(C5,6),1)</f>
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="D5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="str">
+        <f>RIGHT(LEFT(C6,2),1)</f>
+        <v>1</v>
+      </c>
+      <c r="B6" t="str">
+        <f>LEFT(RIGHT(C6,6),1)</f>
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
         <v>13</v>
       </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="D6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="str">
+        <f>RIGHT(LEFT(C7,2),1)</f>
+        <v>1</v>
+      </c>
+      <c r="B7" t="str">
+        <f>LEFT(RIGHT(C7,6),1)</f>
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
         <v>14</v>
       </c>
-      <c r="B7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="D7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="str">
+        <f>RIGHT(LEFT(C8,2),1)</f>
+        <v>1</v>
+      </c>
+      <c r="B8" t="str">
+        <f>LEFT(RIGHT(C8,6),1)</f>
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
         <v>15</v>
       </c>
-      <c r="B8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="D8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="str">
+        <f>RIGHT(LEFT(C9,2),1)</f>
+        <v>1</v>
+      </c>
+      <c r="B9" t="str">
+        <f>LEFT(RIGHT(C9,6),1)</f>
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
         <v>16</v>
       </c>
-      <c r="B9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="D9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="str">
+        <f>RIGHT(LEFT(C10,2),1)</f>
+        <v>1</v>
+      </c>
+      <c r="B10" t="str">
+        <f>LEFT(RIGHT(C10,6),1)</f>
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
         <v>17</v>
       </c>
-      <c r="B10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="D10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="str">
+        <f>RIGHT(LEFT(C11,2),1)</f>
+        <v>1</v>
+      </c>
+      <c r="B11" t="str">
+        <f>LEFT(RIGHT(C11,6),1)</f>
+        <v>6</v>
+      </c>
+      <c r="C11" t="s">
         <v>18</v>
       </c>
-      <c r="B11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="D11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="str">
+        <f>RIGHT(LEFT(C12,2),1)</f>
+        <v>1</v>
+      </c>
+      <c r="B12" t="str">
+        <f>LEFT(RIGHT(C12,6),1)</f>
+        <v>6</v>
+      </c>
+      <c r="C12" t="s">
         <v>19</v>
       </c>
-      <c r="B12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="D12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="str">
+        <f>RIGHT(LEFT(C13,2),1)</f>
+        <v>1</v>
+      </c>
+      <c r="B13" t="str">
+        <f>LEFT(RIGHT(C13,6),1)</f>
+        <v>6</v>
+      </c>
+      <c r="C13" t="s">
         <v>20</v>
       </c>
-      <c r="B13" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="D13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="str">
+        <f>RIGHT(LEFT(C14,2),1)</f>
+        <v>1</v>
+      </c>
+      <c r="B14" t="str">
+        <f>LEFT(RIGHT(C14,6),1)</f>
+        <v>6</v>
+      </c>
+      <c r="C14" t="s">
         <v>21</v>
       </c>
-      <c r="B14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="D14" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="str">
+        <f>RIGHT(LEFT(C15,2),1)</f>
+        <v>1</v>
+      </c>
+      <c r="B15" t="str">
+        <f>LEFT(RIGHT(C15,6),1)</f>
+        <v>6</v>
+      </c>
+      <c r="C15" t="s">
         <v>22</v>
       </c>
-      <c r="B15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="D15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="str">
+        <f>RIGHT(LEFT(C16,2),1)</f>
+        <v>1</v>
+      </c>
+      <c r="B16" t="str">
+        <f>LEFT(RIGHT(C16,6),1)</f>
+        <v>6</v>
+      </c>
+      <c r="C16" t="s">
         <v>23</v>
       </c>
-      <c r="B16" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="D16" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="str">
+        <f>RIGHT(LEFT(C17,2),1)</f>
+        <v>1</v>
+      </c>
+      <c r="B17" t="str">
+        <f>LEFT(RIGHT(C17,6),1)</f>
+        <v>6</v>
+      </c>
+      <c r="C17" t="s">
         <v>24</v>
       </c>
-      <c r="B17" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="D17" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="str">
+        <f>RIGHT(LEFT(C18,2),1)</f>
+        <v>1</v>
+      </c>
+      <c r="B18" t="str">
+        <f>LEFT(RIGHT(C18,6),1)</f>
+        <v>6</v>
+      </c>
+      <c r="C18" t="s">
         <v>25</v>
       </c>
-      <c r="B18" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="D18" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="str">
+        <f>RIGHT(LEFT(C19,2),1)</f>
+        <v>1</v>
+      </c>
+      <c r="B19" t="str">
+        <f>LEFT(RIGHT(C19,6),1)</f>
+        <v>6</v>
+      </c>
+      <c r="C19" t="s">
         <v>26</v>
       </c>
-      <c r="B19" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="D19" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="str">
+        <f>RIGHT(LEFT(C20,2),1)</f>
+        <v>1</v>
+      </c>
+      <c r="B20" t="str">
+        <f>LEFT(RIGHT(C20,6),1)</f>
+        <v>6</v>
+      </c>
+      <c r="C20" t="s">
         <v>27</v>
       </c>
-      <c r="B20" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="D20" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="str">
+        <f>RIGHT(LEFT(C21,2),1)</f>
+        <v>1</v>
+      </c>
+      <c r="B21" t="str">
+        <f>LEFT(RIGHT(C21,6),1)</f>
+        <v>6</v>
+      </c>
+      <c r="C21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="str">
+        <f>RIGHT(LEFT(C22,2),1)</f>
+        <v>1</v>
+      </c>
+      <c r="B22" t="str">
+        <f>LEFT(RIGHT(C22,6),1)</f>
+        <v>6</v>
+      </c>
+      <c r="C22" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="str">
+        <f>RIGHT(LEFT(C23,2),1)</f>
+        <v>2</v>
+      </c>
+      <c r="B23" t="str">
+        <f>LEFT(RIGHT(C23,6),1)</f>
+        <v>2</v>
+      </c>
+      <c r="C23" t="s">
         <v>28</v>
       </c>
-      <c r="B21" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="D23" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="str">
+        <f>RIGHT(LEFT(C24,2),1)</f>
+        <v>2</v>
+      </c>
+      <c r="B24" t="str">
+        <f>LEFT(RIGHT(C24,6),1)</f>
+        <v>2</v>
+      </c>
+      <c r="C24" t="s">
         <v>29</v>
       </c>
-      <c r="B22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="D24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="str">
+        <f>RIGHT(LEFT(C25,2),1)</f>
+        <v>2</v>
+      </c>
+      <c r="B25" t="str">
+        <f>LEFT(RIGHT(C25,6),1)</f>
+        <v>2</v>
+      </c>
+      <c r="C25" t="s">
         <v>30</v>
       </c>
-      <c r="B23" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="D25" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="str">
+        <f>RIGHT(LEFT(C26,2),1)</f>
+        <v>2</v>
+      </c>
+      <c r="B26" t="str">
+        <f>LEFT(RIGHT(C26,6),1)</f>
+        <v>2</v>
+      </c>
+      <c r="C26" t="s">
         <v>31</v>
       </c>
-      <c r="B24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="D26" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="str">
+        <f>RIGHT(LEFT(C27,2),1)</f>
+        <v>2</v>
+      </c>
+      <c r="B27" t="str">
+        <f>LEFT(RIGHT(C27,6),1)</f>
+        <v>2</v>
+      </c>
+      <c r="C27" t="s">
         <v>32</v>
       </c>
-      <c r="B25" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="D27" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="str">
+        <f>RIGHT(LEFT(C28,2),1)</f>
+        <v>2</v>
+      </c>
+      <c r="B28" t="str">
+        <f>LEFT(RIGHT(C28,6),1)</f>
+        <v>2</v>
+      </c>
+      <c r="C28" t="s">
         <v>33</v>
       </c>
-      <c r="B26" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="D28" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="str">
+        <f>RIGHT(LEFT(C29,2),1)</f>
+        <v>2</v>
+      </c>
+      <c r="B29" t="str">
+        <f>LEFT(RIGHT(C29,6),1)</f>
+        <v>2</v>
+      </c>
+      <c r="C29" t="s">
+        <v>60</v>
+      </c>
+      <c r="D29" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="str">
+        <f>RIGHT(LEFT(C30,2),1)</f>
+        <v>2</v>
+      </c>
+      <c r="B30" t="str">
+        <f>LEFT(RIGHT(C30,6),1)</f>
+        <v>2</v>
+      </c>
+      <c r="C30" t="s">
+        <v>61</v>
+      </c>
+      <c r="D30" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="str">
+        <f>RIGHT(LEFT(C31,2),1)</f>
+        <v>2</v>
+      </c>
+      <c r="B31" t="str">
+        <f>LEFT(RIGHT(C31,6),1)</f>
+        <v>2</v>
+      </c>
+      <c r="C31" t="s">
+        <v>62</v>
+      </c>
+      <c r="D31" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="str">
+        <f>RIGHT(LEFT(C32,2),1)</f>
+        <v>3</v>
+      </c>
+      <c r="B32" t="str">
+        <f>LEFT(RIGHT(C32,6),1)</f>
+        <v>4</v>
+      </c>
+      <c r="C32" t="s">
         <v>34</v>
       </c>
-      <c r="B27" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="D32" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="str">
+        <f>RIGHT(LEFT(C33,2),1)</f>
+        <v>3</v>
+      </c>
+      <c r="B33" t="str">
+        <f>LEFT(RIGHT(C33,6),1)</f>
+        <v>4</v>
+      </c>
+      <c r="C33" t="s">
         <v>35</v>
       </c>
-      <c r="B28" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="D33" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="str">
+        <f>RIGHT(LEFT(C34,2),1)</f>
+        <v>3</v>
+      </c>
+      <c r="B34" t="str">
+        <f>LEFT(RIGHT(C34,6),1)</f>
+        <v>4</v>
+      </c>
+      <c r="C34" t="s">
         <v>36</v>
       </c>
-      <c r="B29" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="D34" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="str">
+        <f>RIGHT(LEFT(C35,2),1)</f>
+        <v>3</v>
+      </c>
+      <c r="B35" t="str">
+        <f>LEFT(RIGHT(C35,6),1)</f>
+        <v>4</v>
+      </c>
+      <c r="C35" t="s">
         <v>37</v>
       </c>
-      <c r="B30" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="D35" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="str">
+        <f>RIGHT(LEFT(C36,2),1)</f>
+        <v>3</v>
+      </c>
+      <c r="B36" t="str">
+        <f>LEFT(RIGHT(C36,6),1)</f>
+        <v>4</v>
+      </c>
+      <c r="C36" t="s">
+        <v>63</v>
+      </c>
+      <c r="D36" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="str">
+        <f>RIGHT(LEFT(C37,2),1)</f>
+        <v>3</v>
+      </c>
+      <c r="B37" t="str">
+        <f>LEFT(RIGHT(C37,6),1)</f>
+        <v>4</v>
+      </c>
+      <c r="C37" t="s">
+        <v>64</v>
+      </c>
+      <c r="D37" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="str">
+        <f>RIGHT(LEFT(C38,2),1)</f>
+        <v>4</v>
+      </c>
+      <c r="B38" t="str">
+        <f>LEFT(RIGHT(C38,6),1)</f>
+        <v>5</v>
+      </c>
+      <c r="C38" t="s">
         <v>38</v>
       </c>
-      <c r="B31" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="D38" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="str">
+        <f>RIGHT(LEFT(C39,2),1)</f>
+        <v>4</v>
+      </c>
+      <c r="B39" t="str">
+        <f>LEFT(RIGHT(C39,6),1)</f>
+        <v>5</v>
+      </c>
+      <c r="C39" t="s">
         <v>39</v>
       </c>
-      <c r="B32" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="D39" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="str">
+        <f>RIGHT(LEFT(C40,2),1)</f>
+        <v>4</v>
+      </c>
+      <c r="B40" t="str">
+        <f>LEFT(RIGHT(C40,6),1)</f>
+        <v>5</v>
+      </c>
+      <c r="C40" t="s">
         <v>40</v>
       </c>
-      <c r="B33" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="D40" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="str">
+        <f>RIGHT(LEFT(C41,2),1)</f>
+        <v>4</v>
+      </c>
+      <c r="B41" t="str">
+        <f>LEFT(RIGHT(C41,6),1)</f>
+        <v>5</v>
+      </c>
+      <c r="C41" t="s">
         <v>41</v>
       </c>
-      <c r="B34" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="D41" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="str">
+        <f>RIGHT(LEFT(C42,2),1)</f>
+        <v>4</v>
+      </c>
+      <c r="B42" t="str">
+        <f>LEFT(RIGHT(C42,6),1)</f>
+        <v>5</v>
+      </c>
+      <c r="C42" t="s">
+        <v>65</v>
+      </c>
+      <c r="D42" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="str">
+        <f>RIGHT(LEFT(C43,2),1)</f>
+        <v>4</v>
+      </c>
+      <c r="B43" t="str">
+        <f>LEFT(RIGHT(C43,6),1)</f>
+        <v>5</v>
+      </c>
+      <c r="C43" t="s">
+        <v>66</v>
+      </c>
+      <c r="D43" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="str">
+        <f>RIGHT(LEFT(C44,2),1)</f>
+        <v>5</v>
+      </c>
+      <c r="B44" t="str">
+        <f>LEFT(RIGHT(C44,6),1)</f>
+        <v>4</v>
+      </c>
+      <c r="C44" t="s">
         <v>42</v>
       </c>
-      <c r="B35" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="D44" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="str">
+        <f>RIGHT(LEFT(C45,2),1)</f>
+        <v>5</v>
+      </c>
+      <c r="B45" t="str">
+        <f>LEFT(RIGHT(C45,6),1)</f>
+        <v>4</v>
+      </c>
+      <c r="C45" t="s">
         <v>43</v>
       </c>
-      <c r="B36" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="D45" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="str">
+        <f>RIGHT(LEFT(C46,2),1)</f>
+        <v>5</v>
+      </c>
+      <c r="B46" t="str">
+        <f>LEFT(RIGHT(C46,6),1)</f>
+        <v>4</v>
+      </c>
+      <c r="C46" t="s">
         <v>44</v>
       </c>
-      <c r="B37" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="D46" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="str">
+        <f>RIGHT(LEFT(C47,2),1)</f>
+        <v>5</v>
+      </c>
+      <c r="B47" t="str">
+        <f>LEFT(RIGHT(C47,6),1)</f>
+        <v>4</v>
+      </c>
+      <c r="C47" t="s">
         <v>45</v>
       </c>
-      <c r="B38" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="D47" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="str">
+        <f>RIGHT(LEFT(C48,2),1)</f>
+        <v>5</v>
+      </c>
+      <c r="B48" t="str">
+        <f>LEFT(RIGHT(C48,6),1)</f>
+        <v>4</v>
+      </c>
+      <c r="C48" t="s">
+        <v>67</v>
+      </c>
+      <c r="D48" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" t="str">
+        <f>RIGHT(LEFT(C49,2),1)</f>
+        <v>5</v>
+      </c>
+      <c r="B49" t="str">
+        <f>LEFT(RIGHT(C49,6),1)</f>
+        <v>4</v>
+      </c>
+      <c r="C49" t="s">
+        <v>68</v>
+      </c>
+      <c r="D49" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="str">
+        <f>RIGHT(LEFT(C50,2),1)</f>
+        <v>6</v>
+      </c>
+      <c r="B50" t="str">
+        <f>LEFT(RIGHT(C50,6),1)</f>
+        <v>4</v>
+      </c>
+      <c r="C50" t="s">
         <v>46</v>
       </c>
-      <c r="B39" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="D50" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="str">
+        <f>RIGHT(LEFT(C51,2),1)</f>
+        <v>6</v>
+      </c>
+      <c r="B51" t="str">
+        <f>LEFT(RIGHT(C51,6),1)</f>
+        <v>4</v>
+      </c>
+      <c r="C51" t="s">
         <v>47</v>
       </c>
-      <c r="B40" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="D51" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="str">
+        <f>RIGHT(LEFT(C52,2),1)</f>
+        <v>6</v>
+      </c>
+      <c r="B52" t="str">
+        <f>LEFT(RIGHT(C52,6),1)</f>
+        <v>4</v>
+      </c>
+      <c r="C52" t="s">
         <v>48</v>
       </c>
-      <c r="B41" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="D52" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" t="str">
+        <f>RIGHT(LEFT(C53,2),1)</f>
+        <v>6</v>
+      </c>
+      <c r="B53" t="str">
+        <f>LEFT(RIGHT(C53,6),1)</f>
+        <v>4</v>
+      </c>
+      <c r="C53" t="s">
         <v>49</v>
       </c>
-      <c r="B42" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+      <c r="D53" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" t="str">
+        <f>RIGHT(LEFT(C54,2),1)</f>
+        <v>6</v>
+      </c>
+      <c r="B54" t="str">
+        <f>LEFT(RIGHT(C54,6),1)</f>
+        <v>4</v>
+      </c>
+      <c r="C54" t="s">
+        <v>69</v>
+      </c>
+      <c r="D54" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" t="str">
+        <f>RIGHT(LEFT(C55,2),1)</f>
+        <v>6</v>
+      </c>
+      <c r="B55" t="str">
+        <f>LEFT(RIGHT(C55,6),1)</f>
+        <v>4</v>
+      </c>
+      <c r="C55" t="s">
+        <v>70</v>
+      </c>
+      <c r="D55" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" t="str">
+        <f>RIGHT(LEFT(C56,2),1)</f>
+        <v>7</v>
+      </c>
+      <c r="B56" t="str">
+        <f>LEFT(RIGHT(C56,6),1)</f>
+        <v>6</v>
+      </c>
+      <c r="C56" t="s">
         <v>50</v>
       </c>
-      <c r="B43" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+      <c r="D56" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" t="str">
+        <f>RIGHT(LEFT(C57,2),1)</f>
+        <v>7</v>
+      </c>
+      <c r="B57" t="str">
+        <f>LEFT(RIGHT(C57,6),1)</f>
+        <v>6</v>
+      </c>
+      <c r="C57" t="s">
         <v>51</v>
       </c>
-      <c r="B44" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+      <c r="D57" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" t="str">
+        <f>RIGHT(LEFT(C58,2),1)</f>
+        <v>7</v>
+      </c>
+      <c r="B58" t="str">
+        <f>LEFT(RIGHT(C58,6),1)</f>
+        <v>6</v>
+      </c>
+      <c r="C58" t="s">
+        <v>54</v>
+      </c>
+      <c r="D58" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" t="str">
+        <f>RIGHT(LEFT(C59,2),1)</f>
+        <v>7</v>
+      </c>
+      <c r="B59" t="str">
+        <f>LEFT(RIGHT(C59,6),1)</f>
+        <v>6</v>
+      </c>
+      <c r="C59" t="s">
+        <v>55</v>
+      </c>
+      <c r="D59" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" t="str">
+        <f>RIGHT(LEFT(C60,2),1)</f>
+        <v>7</v>
+      </c>
+      <c r="B60" t="str">
+        <f>LEFT(RIGHT(C60,6),1)</f>
+        <v>6</v>
+      </c>
+      <c r="C60" t="s">
+        <v>71</v>
+      </c>
+      <c r="D60" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" t="str">
+        <f>RIGHT(LEFT(C61,2),1)</f>
+        <v>7</v>
+      </c>
+      <c r="B61" t="str">
+        <f>LEFT(RIGHT(C61,6),1)</f>
+        <v>6</v>
+      </c>
+      <c r="C61" t="s">
+        <v>73</v>
+      </c>
+      <c r="D61" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" t="str">
+        <f>RIGHT(LEFT(C62,2),1)</f>
+        <v>8</v>
+      </c>
+      <c r="B62" t="str">
+        <f>LEFT(RIGHT(C62,6),1)</f>
+        <v>4</v>
+      </c>
+      <c r="C62" t="s">
         <v>52</v>
       </c>
-      <c r="B45" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+      <c r="D62" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" t="str">
+        <f>RIGHT(LEFT(C63,2),1)</f>
+        <v>8</v>
+      </c>
+      <c r="B63" t="str">
+        <f>LEFT(RIGHT(C63,6),1)</f>
+        <v>4</v>
+      </c>
+      <c r="C63" t="s">
         <v>53</v>
       </c>
-      <c r="B46" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>54</v>
-      </c>
-      <c r="B47" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>55</v>
-      </c>
-      <c r="B48" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+      <c r="D63" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" t="str">
+        <f>RIGHT(LEFT(C64,2),1)</f>
+        <v>8</v>
+      </c>
+      <c r="B64" t="str">
+        <f>LEFT(RIGHT(C64,6),1)</f>
+        <v>4</v>
+      </c>
+      <c r="C64" t="s">
         <v>56</v>
       </c>
-      <c r="B49" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+      <c r="D64" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" t="str">
+        <f>RIGHT(LEFT(C65,2),1)</f>
+        <v>8</v>
+      </c>
+      <c r="B65" t="str">
+        <f>LEFT(RIGHT(C65,6),1)</f>
+        <v>4</v>
+      </c>
+      <c r="C65" t="s">
         <v>57</v>
       </c>
-      <c r="B50" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>58</v>
-      </c>
-      <c r="B51" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>59</v>
-      </c>
-      <c r="B52" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>60</v>
-      </c>
-      <c r="B53" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>61</v>
-      </c>
-      <c r="B54" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>62</v>
-      </c>
-      <c r="B55" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>63</v>
-      </c>
-      <c r="B56" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>64</v>
-      </c>
-      <c r="B57" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>65</v>
-      </c>
-      <c r="B58" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>66</v>
-      </c>
-      <c r="B59" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>67</v>
-      </c>
-      <c r="B60" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>68</v>
-      </c>
-      <c r="B61" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>69</v>
-      </c>
-      <c r="B62" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>70</v>
-      </c>
-      <c r="B63" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>71</v>
-      </c>
-      <c r="B64" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+      <c r="D65" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" t="str">
+        <f>RIGHT(LEFT(C66,2),1)</f>
+        <v>8</v>
+      </c>
+      <c r="B66" t="str">
+        <f>LEFT(RIGHT(C66,6),1)</f>
+        <v>4</v>
+      </c>
+      <c r="C66" t="s">
         <v>72</v>
       </c>
-      <c r="B65" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>73</v>
-      </c>
-      <c r="B66" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+      <c r="D66" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" t="str">
+        <f>RIGHT(LEFT(C67,2),1)</f>
+        <v>8</v>
+      </c>
+      <c r="B67" t="str">
+        <f>LEFT(RIGHT(C67,6),1)</f>
+        <v>4</v>
+      </c>
+      <c r="C67" t="s">
         <v>74</v>
       </c>
-      <c r="B67" t="s">
-        <v>8</v>
+      <c r="D67" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D67">
+    <sortCondition ref="A2:A67"/>
+    <sortCondition ref="B2:B67"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="containsText" priority="1" operator="containsText" id="{7A67E0E9-BC46-4111-B070-728168ED54EB}">
-            <xm:f>NOT(ISERROR(SEARCH(Dropdown_options!$A$2,B2)))</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH(Dropdown_options!$A$2,D2)))</xm:f>
             <xm:f>Dropdown_options!$A$2</xm:f>
             <x14:dxf>
               <font>
@@ -2332,7 +2870,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="containsText" priority="2" operator="containsText" id="{F891952C-C388-4833-AD9E-FF872CD81D43}">
-            <xm:f>NOT(ISERROR(SEARCH(Dropdown_options!$A$5,B2)))</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH(Dropdown_options!$A$5,D2)))</xm:f>
             <xm:f>Dropdown_options!$A$5</xm:f>
             <x14:dxf>
               <font>
@@ -2346,7 +2884,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="containsText" priority="3" operator="containsText" id="{0400A822-BD6D-4266-93F8-1991FC29458D}">
-            <xm:f>NOT(ISERROR(SEARCH(Dropdown_options!$A$3,B2)))</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH(Dropdown_options!$A$3,D2)))</xm:f>
             <xm:f>Dropdown_options!$A$3</xm:f>
             <x14:dxf>
               <font>
@@ -2360,7 +2898,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="containsText" priority="4" operator="containsText" id="{D90AEFBD-B16A-404D-B9FE-6C2E8EA5536C}">
-            <xm:f>NOT(ISERROR(SEARCH(Dropdown_options!$A$4,B2)))</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH(Dropdown_options!$A$4,D2)))</xm:f>
             <xm:f>Dropdown_options!$A$4</xm:f>
             <x14:dxf>
               <font>
@@ -2373,7 +2911,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>B2:B1048576</xm:sqref>
+          <xm:sqref>D2:D1048576</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -2383,7 +2921,7 @@
           <x14:formula1>
             <xm:f>Dropdown_options!$A$2:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B67</xm:sqref>
+          <xm:sqref>D2:D67</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
